--- a/SGC-CKN/Excel/037ded6f-8d3f-4977-b85c-323d3ef9338f_Lô_CT-02_P7-110_D800_26-03-2026.xlsx
+++ b/SGC-CKN/Excel/037ded6f-8d3f-4977-b85c-323d3ef9338f_Lô_CT-02_P7-110_D800_26-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>21:45 26/03/2026</t>
+    <t>21:35 26/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -203,7 +203,7 @@
 26/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:50
+    <t xml:space="preserve">16:30
 26/03/2026</t>
   </si>
   <si>
@@ -231,7 +231,7 @@
 26/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">21:45
+    <t xml:space="preserve">21:35
 26/03/2026</t>
   </si>
   <si>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.51</v>
@@ -1262,10 +1262,10 @@
         <v>0.5</v>
       </c>
       <c r="I11" s="5">
-        <v>3.86</v>
+        <v>7.51</v>
       </c>
       <c r="J11" s="8">
-        <v>7.72</v>
+        <v>15.02</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1291,16 +1291,16 @@
         <v>-7.51</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.12</v>
+        <v>-9.42</v>
       </c>
       <c r="H12" s="9">
         <v>0.48</v>
       </c>
       <c r="I12" s="9">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="J12" s="12">
-        <v>3.33</v>
+        <v>3.95</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1323,19 +1323,19 @@
         <v>38</v>
       </c>
       <c r="F13" s="13">
-        <v>-9.12</v>
+        <v>-9.42</v>
       </c>
       <c r="G13" s="13">
-        <v>-10.84</v>
+        <v>-17.34</v>
       </c>
       <c r="H13" s="13">
         <v>0.67</v>
       </c>
       <c r="I13" s="13">
-        <v>1.72</v>
-      </c>
-      <c r="J13" s="12">
-        <v>2.58</v>
+        <v>7.92</v>
+      </c>
+      <c r="J13" s="8">
+        <v>11.88</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1358,19 +1358,19 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>-10.84</v>
+        <v>-17.34</v>
       </c>
       <c r="G14" s="16">
-        <v>-21.42</v>
+        <v>-21.12</v>
       </c>
       <c r="H14" s="16">
         <v>0.65</v>
       </c>
       <c r="I14" s="16">
-        <v>10.58</v>
+        <v>3.78</v>
       </c>
       <c r="J14" s="8">
-        <v>16.28</v>
+        <v>5.82</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1393,7 +1393,7 @@
         <v>46</v>
       </c>
       <c r="F15" s="19">
-        <v>-21.42</v>
+        <v>-21.12</v>
       </c>
       <c r="G15" s="19">
         <v>-25.11</v>
@@ -1402,10 +1402,10 @@
         <v>0.65</v>
       </c>
       <c r="I15" s="19">
-        <v>3.69</v>
+        <v>3.99</v>
       </c>
       <c r="J15" s="8">
-        <v>5.68</v>
+        <v>6.14</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1466,16 +1466,16 @@
         <v>-35.01</v>
       </c>
       <c r="G17" s="25">
-        <v>-37.7</v>
+        <v>-37.3</v>
       </c>
       <c r="H17" s="25">
         <v>0.47</v>
       </c>
       <c r="I17" s="25">
-        <v>2.69</v>
-      </c>
-      <c r="J17" s="8">
-        <v>5.76</v>
+        <v>2.29</v>
+      </c>
+      <c r="J17" s="12">
+        <v>4.91</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1498,19 +1498,19 @@
         <v>58</v>
       </c>
       <c r="F18" s="28">
-        <v>-37.7</v>
+        <v>-37.3</v>
       </c>
       <c r="G18" s="28">
         <v>-39</v>
       </c>
       <c r="H18" s="28">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="I18" s="28">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J18" s="12">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1574,13 +1574,13 @@
         <v>-45.01</v>
       </c>
       <c r="H20" s="34">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="I20" s="34">
         <v>1.11</v>
       </c>
       <c r="J20" s="37">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1735,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.51</v>
@@ -1744,10 +1744,10 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="5">
-        <v>3.86</v>
+        <v>7.51</v>
       </c>
       <c r="I2" s="8">
-        <v>7.72</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1767,16 +1767,16 @@
         <v>-7.51</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.12</v>
+        <v>-9.42</v>
       </c>
       <c r="G3" s="9">
         <v>0.48</v>
       </c>
       <c r="H3" s="9">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="I3" s="12">
-        <v>3.33</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1793,19 +1793,19 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>-9.12</v>
+        <v>-9.42</v>
       </c>
       <c r="F4" s="13">
-        <v>-10.84</v>
+        <v>-17.34</v>
       </c>
       <c r="G4" s="13">
         <v>0.67</v>
       </c>
       <c r="H4" s="13">
-        <v>1.72</v>
-      </c>
-      <c r="I4" s="12">
-        <v>2.58</v>
+        <v>7.92</v>
+      </c>
+      <c r="I4" s="8">
+        <v>11.88</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1822,19 +1822,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>-10.84</v>
+        <v>-17.34</v>
       </c>
       <c r="F5" s="16">
-        <v>-21.42</v>
+        <v>-21.12</v>
       </c>
       <c r="G5" s="16">
         <v>0.65</v>
       </c>
       <c r="H5" s="16">
-        <v>10.58</v>
+        <v>3.78</v>
       </c>
       <c r="I5" s="8">
-        <v>16.28</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1851,7 +1851,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>-21.42</v>
+        <v>-21.12</v>
       </c>
       <c r="F6" s="19">
         <v>-25.11</v>
@@ -1860,10 +1860,10 @@
         <v>0.65</v>
       </c>
       <c r="H6" s="19">
-        <v>3.69</v>
+        <v>3.99</v>
       </c>
       <c r="I6" s="8">
-        <v>5.68</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1912,16 +1912,16 @@
         <v>-35.01</v>
       </c>
       <c r="F8" s="25">
-        <v>-37.7</v>
+        <v>-37.3</v>
       </c>
       <c r="G8" s="25">
         <v>0.47</v>
       </c>
       <c r="H8" s="25">
-        <v>2.69</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5.76</v>
+        <v>2.29</v>
+      </c>
+      <c r="I8" s="12">
+        <v>4.91</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1938,19 +1938,19 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.7</v>
+        <v>-37.3</v>
       </c>
       <c r="F9" s="28">
         <v>-39</v>
       </c>
       <c r="G9" s="28">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="28">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="I9" s="12">
-        <v>1.56</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2002,13 +2002,13 @@
         <v>-45.01</v>
       </c>
       <c r="G11" s="34">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="H11" s="34">
         <v>1.11</v>
       </c>
       <c r="I11" s="37">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2025,19 +2025,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-3.65</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-45.01</v>
       </c>
       <c r="G12" s="40">
-        <v>9.45</v>
+        <v>8.95</v>
       </c>
       <c r="H12" s="40">
-        <v>41.36</v>
+        <v>45.01</v>
       </c>
       <c r="I12" s="40">
-        <v>4.38</v>
+        <v>5.03</v>
       </c>
     </row>
   </sheetData>
